--- a/data files/Draft - Kensington Health Criteria Feedback (Responses).xlsx
+++ b/data files/Draft - Kensington Health Criteria Feedback (Responses).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="94">
   <si>
     <t>Timestamp</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>Committee Membership</t>
+  </si>
+  <si>
+    <t>OR Time Elsewhere</t>
   </si>
 </sst>
 </file>
@@ -427,7 +430,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:CI5" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:CI11" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="87">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="Among the listed criteria, which is the MOST IMPORTANT (BEST) criterion when deciding physicians' scheduling priorities?" id="2"/>
@@ -1250,6 +1253,288 @@
         <v>6.0</v>
       </c>
     </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="5">
+        <v>46163.47963666667</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA6" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="AB6" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="AC6" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="AS6" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT6" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="AU6" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="AV6" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="AW6" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="AX6" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="AY6" s="6">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="5">
+        <v>46163.482214675925</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="U7" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="V7" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="W7" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="X7" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="Y7" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="Z7" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="AS7" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BL7" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="BM7" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="BN7" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="BO7" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="BP7" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="BQ7" s="6">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="5">
+        <v>46163.48257903935</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="O8" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="P8" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="R8" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S8" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="T8" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="AS8" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AZ8" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="BA8" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="BB8" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="BC8" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="BD8" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="BE8" s="6">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="5">
+        <v>46163.48290212963</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="J9" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="K9" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="L9" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="M9" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="N9" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="AS9" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AZ9" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="BA9" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="BB9" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="BC9" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="BD9" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="BE9" s="6">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="5">
+        <v>46163.48324528935</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG10" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="AH10" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="AI10" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="AJ10" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="AK10" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="AL10" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="AS10" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="BR10" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="BS10" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="BT10" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="BU10" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="BV10" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="BW10" s="6">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="5">
+        <v>46163.48486332176</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA11" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="AB11" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="AC11" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="AD11" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="AE11" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="AF11" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="AS11" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="BF11" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="BG11" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="BH11" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="BI11" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="BJ11" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="BK11" s="6">
+        <v>5.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
   <tableParts count="1">
